--- a/SampleData/Sample Data for Recommender System.xlsx
+++ b/SampleData/Sample Data for Recommender System.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="208">
   <si>
     <t>Drug Name.1</t>
   </si>
@@ -395,15 +395,263 @@
   </si>
   <si>
     <t>Had occasional palpatations previously that was told it was due to thyroid meds. Woke up one morning in afib. In the ER my heart rate was 175-200. Converted immediately with cardizem. Was put on lultaq 400mg 2X day. After 6 weeks I developed a rash &amp; hives on my arms, neck and side of my face. I'm waiting to hear what they are going to switch me to.</t>
+  </si>
+  <si>
+    <t>debacterol swab, medicated</t>
+  </si>
+  <si>
+    <t>10/22/2008</t>
+  </si>
+  <si>
+    <t>Canker Sore</t>
+  </si>
+  <si>
+    <t>I am a nurse in a family clinic setting. We keep Debacterol on hand to use on our patients with excellent results. Patients return stating that nothing else has ever worked as well as Debacterol.</t>
+  </si>
+  <si>
+    <t>diovan</t>
+  </si>
+  <si>
+    <t>8/31/2011</t>
+  </si>
+  <si>
+    <t>High Blood Pressure</t>
+  </si>
+  <si>
+    <t>dizziness, fainting spells, more thirsty even though i drink a lot of water, and sick on the stomach.</t>
+  </si>
+  <si>
+    <t>diovan hct</t>
+  </si>
+  <si>
+    <t>I was taking Diovan 160 BP was at 120/90. Doctor switched me to 320/12.5 and blood pressure now regularly at 130/80. Not sure why the increase in the systolic number, but the doctor hasn't been concerned.
+ Other than that the medicine has worked better than the 160 with few if any side effects. Actually with working out and eating properly I have experienced weight loss.</t>
+  </si>
+  <si>
+    <t>depakote</t>
+  </si>
+  <si>
+    <t>9/30/2009</t>
+  </si>
+  <si>
+    <t>I was prescribed Depakote for anger and impulse control....has worked great for that but having terrible shaking episodes, anxious feelings, and palpitations...I am quitting....</t>
+  </si>
+  <si>
+    <t>I read some of the reviews on here and was really scared to use this product but had a really sore canker sore that was making eating and even talking painful. My dentist gave me a prescription but I hadn't used it because I was afraid of how much it would hurt. I just used it for the first time about 5 minutes ago and am THRILLED with this product. First of all the pain was really not bad at all. I think using one of those numbing agents like anbesol gel actually hurts a lot more and they are only temporary. I am definitely going to get another prescription for this. What a relief to finally have an answer for all those horrible canker sores. I wish I had found this ages ago and highly recommend it to anyone. My canker sore already feels a LOT better.</t>
+  </si>
+  <si>
+    <t>My dentist applied Debacterol to a very sore ulcer in my mouth. It hurt breifly but then no more pain or discomfort. I suffer from these ulcers frequently so this is a very welcome drug.</t>
+  </si>
+  <si>
+    <t>5/13/2008</t>
+  </si>
+  <si>
+    <t>I, like the prior reviewer, have been waiting all my life for a marvel like this. My dentist applied the past and to my amazement, the canker sore was pain free but still visible but within 24 hours, it reduced in size and still no pain. It's been a little over a day and it's almost completely gone! I get real bad outbreaks 5-6 at a time and some on my tongue, inner lip, and gum. I also get them on my throat but the dentist said that it's not a good idea to treat those but I'm glad I got rid of all the ones they were able to. TRY THIS ONCE!!! ASK FOR IT!!!</t>
+  </si>
+  <si>
+    <t>The evening after my first dose of 80 mg of this drug, I began to develop blister like very itchy hives on my wrist, moving to my forearm, then after 5 days to my thighs. But it did lower my blood pressure. I have been switched to Norvasc and hope it works without side effects.</t>
+  </si>
+  <si>
+    <t>7/19/2008</t>
+  </si>
+  <si>
+    <t>The drug lowers my blood pressure but causes extreme, insatiable thirst.</t>
+  </si>
+  <si>
+    <t>Manic-Depression</t>
+  </si>
+  <si>
+    <t>sores in mouth, sore throat. Tried 3 different times with the same result each time.</t>
+  </si>
+  <si>
+    <t>Bipolar I Disorder with Most Recent Episode Mixed</t>
+  </si>
+  <si>
+    <t>Although depokote did help me I was on it for 7 years. I was up to 2500 mg a day and it gave me bowel problems I would not wish on anyone. My first priority was knowing where a bathroom was and carried air freshener in my purse. (sorry graphic I know) Thank god the Doc took me off that and gave me others that have not given me that nasty side effect.</t>
+  </si>
+  <si>
+    <t>7/30/2011</t>
+  </si>
+  <si>
+    <t>somebody inform me that it causes type 2 diabetis systoms</t>
+  </si>
+  <si>
+    <t>SOME EVENINGS I HAVE B/P OF 99/48 ESPECIALLY WHEN I QUIETLY SIT IN FRONT OF TV.</t>
+  </si>
+  <si>
+    <t>Bipolar Depression</t>
+  </si>
+  <si>
+    <t>The first 2 weeks I was on a twice a day 250mg dose now I take 500mg XR only at night. It has totally changed my life for the better! Bipolar was running my marriage before and this is the first medication I have ever taken for depression. I also take Celexa along with it.</t>
+  </si>
+  <si>
+    <t>7/28/2011</t>
+  </si>
+  <si>
+    <t>I just had a dizzy spell which I think is related to taking Diovan</t>
+  </si>
+  <si>
+    <t>5/29/2008</t>
+  </si>
+  <si>
+    <t>Only on this prescription for 2 wks, went to the dr today. My side affects were feeling like I was running a fever, actually felt like I was catching a cold, with lots of sneezing, I was on a different mood stabilizer that did the same thing. I was still have the mood swings, with unwarranted crying spells.</t>
+  </si>
+  <si>
+    <t>5/28/2008</t>
+  </si>
+  <si>
+    <t>New to Diovan HCT since coughing spells w/Lisinopril. Started on 80mg/12.5mg, but needed to up it to 160/25 due to returning edema. Bloodwork is showing elevated liver enzymes now. Will be seeing MD for this next week. Could be side effect. I also have gained weight around my mid-section. Is this common and how long does it last? I can't afford to gain any extra weight. I'm also hypothyroid &amp; have maintained my weight (albeit not what I would like) for the last 15 years. Recently had a hysterectomy to remove a mass also. I really don't need any more problems.</t>
+  </si>
+  <si>
+    <t>6/26/2010</t>
+  </si>
+  <si>
+    <t>Seizures with Irregular Muscle Contractions</t>
+  </si>
+  <si>
+    <t>Its been rather good for me just always have to make sure I get the needed rest and it really helps with the seizures too..much better and not too much pain.so far reallly satisfied..with the treatment I am taking..</t>
+  </si>
+  <si>
+    <t>7/27/2011</t>
+  </si>
+  <si>
+    <t>I took 80mg a for 30days,dosage was increase to 160 per day because level didn't drop.after about a week i notice little water type bumps on both arms from wrist up to my elbow giving a stinging type effect.Also at times itching sensation overall my body,hoping it just my body adjusting to the dosage.I'm getting concern maybe medication to strong(diovan)no other discomfort,I have call my doctor to reiew my concerns.I pray all well !!!</t>
+  </si>
+  <si>
+    <t>5/27/2008</t>
+  </si>
+  <si>
+    <t>MOST OF THE TIME I DON'T HAVE HEADACHES ANYMORE BUT, IF I DRINK CAFFEINE IN MAJOR QUANTITIES, MY PRESSURE GOES SKY HIGH AND IT TAKES A LONGER THAN NORMAL TIME TO COME BACK DOWN. BEING OBESE MY MOVING AT ALL IS RAISING MY HBP BUT, WITH DIOVAN, I'M NOT FEELING AS BAD AS I USED TO AFTER ALOT OF RUNNING AROUND...WHO KNEW? MY HBP IS STILL HIGH BUT NOT AS BAD AS WHEN I TOOK NORVASC AND LOPRESSOR. I'LL GIVE THIS DIOVAN A FEW MORE WEEKS BEFORE I TRY SOMETHING ELSE OR NOT..THANKS</t>
+  </si>
+  <si>
+    <t>Epileptic Seizure</t>
+  </si>
+  <si>
+    <t>My son began taking this medicine when he was diagnosed with occipital epilepsy at age 3 (he is now 5 1/2). I immediately noticed side effects: his hands became very shaky (to the point where he quite drawing and coloring), he complained of dizziness and had frequent nightmares. After a few months of use, my son would know when it was time to take it because the shaking/dizziness would worsen if we were late or missed a dose. However, it works very well for him. Aside from having to have his blood tested for liver enzymes every 6 months, he has had only two seizures since he began taking it. We have learned to deal with the side effects. He no longer uses coloring books but rather draws freehand so he doesn't have to worry about going outside the lines, and we got a dreamcatcher for his nightmares, and he doesn't complain of bad dreams near as much. Overall, it has been well worth it.</t>
+  </si>
+  <si>
+    <t>7/26/2011</t>
+  </si>
+  <si>
+    <t>5/22/2008</t>
+  </si>
+  <si>
+    <t>6/17/2010</t>
+  </si>
+  <si>
+    <t>Mania associated with Bipolar Disorder</t>
+  </si>
+  <si>
+    <t>This medication almost killed me and I didn't even realize until I was being carted off by the EMTs. Depakote worked great at killing my emotions, but I was highly allergic to it my body started to get so itchy and my throat started to close up. Please trust your intution if you think something is wrong talk to your doctor at once. It would have been great if I hadn't been so allergic to it. Good Luck!!</t>
+  </si>
+  <si>
+    <t>7/15/2011</t>
+  </si>
+  <si>
+    <t>5/21/2008</t>
+  </si>
+  <si>
+    <t>love it! been on diovan hct for 5 years never had a problem.</t>
+  </si>
+  <si>
+    <t>6/16/2010</t>
+  </si>
+  <si>
+    <t>have been on 2000mg depakote/ day for about 2 1/2 years. have noticed no change in depression, although i haven't had a serious manic episode in that time either.also have noticed no side effects. have tried several different meds over past 4 years, with no better luck.i'm currently on 10mg abilify,lorazepam,and ambien when needed. none of which seem effective.</t>
+  </si>
+  <si>
+    <t>7/14/2011</t>
+  </si>
+  <si>
+    <t>5/19/2008</t>
+  </si>
+  <si>
+    <t>6/13/2010</t>
+  </si>
+  <si>
+    <t>I switched from dovan 80 mg cost $85.00 mo.
+ and triam/hctz 37.5/25 tab cost $5.12 mo.after 15 years. to losartan- hctz 59-12.5 mg tab cost $11.27 mo. works even better. why did the doctor put me on such expensive medicine to start. Hope this helps someone. I tried to find out for years what to switch too.</t>
+  </si>
+  <si>
+    <t>I've been taking this med for 3 years and have experienced no adverse side effects whatsoever. My blood pressure is completely controlled. Very expensive on my insurance.</t>
+  </si>
+  <si>
+    <t>9/29/2009</t>
+  </si>
+  <si>
+    <t>dangerous side effects</t>
+  </si>
+  <si>
+    <t>It has been less effective lately. I am going to a higher dose.</t>
+  </si>
+  <si>
+    <t>I am very happy with this medication. I used to be on lithium. I went toxic on lithium and it wasn't very good. The only problem i have is that it makes me have itchy rashes once in a while. My doctor said it is nothing to worry about. I am very happy on Depakote and i have been stable since i started taking it.</t>
+  </si>
+  <si>
+    <t>I am taking the very highest dose of Diovan allowed. It is in addition to two other HBP meds.
+ It does seem to be helpful in controlling my HBP. As a side, I also have a continuing A-fib problem which may be responding better to Diovan.</t>
+  </si>
+  <si>
+    <t>4/21/2008</t>
+  </si>
+  <si>
+    <t>Took it for a week..was difficult to get my mouth to say what my mind was thinking..after 2 weeks the pain in my back, neck and bones became chronic and unbearable...discontiued after 3 weeks and I now feel 'normal'.......wouldn't recommend to anyone</t>
+  </si>
+  <si>
+    <t>Have had an allergic reaction to this medicine in both generic and brand name.</t>
+  </si>
+  <si>
+    <t>6/30/2011</t>
+  </si>
+  <si>
+    <t>I never felt as bad as I do now, I'd rather have the hypertension! I have a dry, hacking cough, like a tickle in my throat constantly and never thought this was a side effect until I came here and saw how many people were complaining of the same thing. The ironic part about it, is that this med makes me feel worse and didn't even lower my BP! I'm going back to Benicar, never had a prob, just switched because it was pricey. I'd rather pay more for a drug and feel better than feel like I do now.</t>
+  </si>
+  <si>
+    <t>It completely eliminated my coughing spells which I experienced with Lotensin.</t>
+  </si>
+  <si>
+    <t>I was misdiagnosed with Bipolar I Disorder. The first Psychiatrist I saw prescribed this to me. I have had my name CLEARED by other Psychiatrist, confirming that I do not even have Bipolar Disorder.
+ As for this medication, this is absolutely garbage. It causes intense weight gain, hair loss, and dulling of emotions. When you take this, you can't remember things as well either, and all creativity is lost. What's worse is, that when taken, it only works temporarily, and then you have to keep increasing the dosage because your body gets used to it. Don't take this medication.</t>
+  </si>
+  <si>
+    <t>dilt-xr</t>
+  </si>
+  <si>
+    <t>10/29/2009</t>
+  </si>
+  <si>
+    <t>Ventricular Rate Control in Atrial Fibrillation</t>
+  </si>
+  <si>
+    <t>my bp is fluxuating up an down....my heart rate gets to slow....i still have palputations all day long With or without this med</t>
+  </si>
+  <si>
+    <t>Dry mouth. I'm constantly thirsty. Also, noticed decrease in hunger.</t>
+  </si>
+  <si>
+    <t>7/24/2009</t>
+  </si>
+  <si>
+    <t>Only problem is it makes me lazy without as much energy and not nearly as high key as I am normally.</t>
+  </si>
+  <si>
+    <t>dilaudid ampul</t>
+  </si>
+  <si>
+    <t>5/14/2011</t>
+  </si>
+  <si>
+    <t>I have several serious medical conditions that each cause VERY sever pain. I also have Gastroparesis, which makes taking pain pills worthless. I get Sub-Q injections every 3hrs and the pain is considerably eased. Nothing can take my pain away, but this is the best it's ever been. I no longer have any side affects, they all go away within a short period.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd-mmm"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -476,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -521,6 +769,12 @@
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -2175,8 +2429,1362 @@
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
     </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G52" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="G53" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="I53" s="11"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="15">
+        <v>39547.0</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I54" s="11"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="G55" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I55" s="11"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="15">
+        <v>39545.0</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G56" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I56" s="11"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="16">
+        <v>39635.0</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="10">
+        <v>4.666666667</v>
+      </c>
+      <c r="G57" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I57" s="11"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G58" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I58" s="11"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" s="15">
+        <v>40824.0</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F59" s="6">
+        <v>1.666666667</v>
+      </c>
+      <c r="G59" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I59" s="11"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F60" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="G60" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="15">
+        <v>40428.0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" s="6">
+        <v>1.333333333</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I61" s="11"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="16">
+        <v>40641.0</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F62" s="10">
+        <v>4.666666667</v>
+      </c>
+      <c r="G62" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="15">
+        <v>39759.0</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="6">
+        <v>3.666666667</v>
+      </c>
+      <c r="G63" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="16">
+        <v>40366.0</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="G64" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I64" s="11"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="6">
+        <v>2.333333333</v>
+      </c>
+      <c r="G65" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I65" s="11"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="16">
+        <v>39698.0</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F66" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="G66" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I66" s="11"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="15">
+        <v>40305.0</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F67" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G67" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I67" s="11"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F68" s="10">
+        <v>4.333333333</v>
+      </c>
+      <c r="G68" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I68" s="11"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" s="6">
+        <v>3.666666667</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="16">
+        <v>40185.0</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F70" s="10">
+        <v>2.666666667</v>
+      </c>
+      <c r="G70" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I70" s="11"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F71" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G71" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F72" s="10">
+        <v>4.333333333</v>
+      </c>
+      <c r="G72" s="10">
+        <v>22.0</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" s="11"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F73" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G73" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I73" s="11"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F74" s="10">
+        <v>3.333333333</v>
+      </c>
+      <c r="G74" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I74" s="11"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F75" s="6">
+        <v>3.333333333</v>
+      </c>
+      <c r="G75" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I75" s="11"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="17">
+        <v>46176.0</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76" s="10">
+        <v>4.666666667</v>
+      </c>
+      <c r="G76" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="I76" s="11"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F77" s="6">
+        <v>4.666666667</v>
+      </c>
+      <c r="G77" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F78" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="G78" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="G79" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I79" s="11"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F80" s="10">
+        <v>3.333333333</v>
+      </c>
+      <c r="G80" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G81" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I81" s="11"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="14"/>
+      <c r="E82" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F82" s="10">
+        <v>2.333333333</v>
+      </c>
+      <c r="G82" s="10">
+        <v>13.0</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I82" s="11"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F83" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G83" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F84" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="G84" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F85" s="6">
+        <v>4.333333333</v>
+      </c>
+      <c r="G85" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="16">
+        <v>40762.0</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F86" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="G86" s="10">
+        <v>11.0</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="I86" s="11"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B87" s="15">
+        <v>39665.0</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F87" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G87" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I87" s="11"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="G88" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I88" s="14"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" s="15">
+        <v>40670.0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F89" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="G89" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F90" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="G90" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I90" s="11"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" s="15">
+        <v>40488.0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F91" s="6">
+        <v>4.666666667</v>
+      </c>
+      <c r="G91" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I91" s="11"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B92" s="16">
+        <v>40550.0</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F92" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="G92" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I92" s="11"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F93" s="6">
+        <v>1.666666667</v>
+      </c>
+      <c r="G93" s="6">
+        <v>32.0</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I93" s="11"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="16">
+        <v>40457.0</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="G94" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F95" s="6">
+        <v>2.333333333</v>
+      </c>
+      <c r="G95" s="6">
+        <v>17.0</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I95" s="11"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="G96" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I96" s="11"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97" s="15">
+        <v>40365.0</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F97" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I97" s="11"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F98" s="10">
+        <v>2.333333333</v>
+      </c>
+      <c r="G98" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="I98" s="11"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="15">
+        <v>39823.0</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="6">
+        <v>4.666666667</v>
+      </c>
+      <c r="G99" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I99" s="11"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F100" s="10">
+        <v>2.666666667</v>
+      </c>
+      <c r="G100" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="I100" s="11"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F101" s="10">
+        <v>4.666666667</v>
+      </c>
+      <c r="G101" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="I101" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="85">
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="H93:I93"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H5:J5"/>
@@ -2212,11 +3820,6 @@
     <mergeCell ref="H36:J36"/>
     <mergeCell ref="H37:J37"/>
     <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H51:J51"/>
     <mergeCell ref="H39:J39"/>
     <mergeCell ref="H40:J40"/>
     <mergeCell ref="H41:J41"/>
@@ -2224,6 +3827,13 @@
     <mergeCell ref="H43:J43"/>
     <mergeCell ref="H45:J45"/>
     <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
